--- a/resources/templates/standard/F2100-15.xlsx
+++ b/resources/templates/standard/F2100-15.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="7">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>숙련도 등급</t>
   </si>
@@ -478,7 +481,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -954,13 +959,13 @@
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
       <c r="AI10" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN10" s="3"/>
       <c r="AO10" s="3"/>
@@ -1011,7 +1016,7 @@
       <c r="AK11" s="4"/>
       <c r="AL11" s="4"/>
       <c r="AM11" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN11" s="5"/>
       <c r="AO11" s="5"/>
@@ -1062,7 +1067,7 @@
       <c r="AK12" s="4"/>
       <c r="AL12" s="4"/>
       <c r="AM12" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN12" s="5"/>
       <c r="AO12" s="5"/>
@@ -1113,7 +1118,7 @@
       <c r="AK13" s="4"/>
       <c r="AL13" s="4"/>
       <c r="AM13" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN13" s="5"/>
       <c r="AO13" s="5"/>
@@ -1121,7 +1126,7 @@
       <c r="AQ13" s="5"/>
       <c r="AR13" s="5"/>
       <c r="AS13" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT13" s="6"/>
       <c r="AU13" s="6"/>
@@ -1211,13 +1216,13 @@
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
@@ -1268,7 +1273,7 @@
       <c r="AK16" s="4"/>
       <c r="AL16" s="4"/>
       <c r="AM16" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
@@ -1319,7 +1324,7 @@
       <c r="AK17" s="4"/>
       <c r="AL17" s="4"/>
       <c r="AM17" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN17" s="5"/>
       <c r="AO17" s="5"/>
@@ -1370,7 +1375,7 @@
       <c r="AK18" s="4"/>
       <c r="AL18" s="4"/>
       <c r="AM18" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN18" s="5"/>
       <c r="AO18" s="5"/>
@@ -1378,7 +1383,7 @@
       <c r="AQ18" s="5"/>
       <c r="AR18" s="5"/>
       <c r="AS18" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT18" s="6"/>
       <c r="AU18" s="6"/>
